--- a/_FACTORY/_LIGNES/_TEMPLATE/B3_DISTRACTEURS/B3_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/B3_DISTRACTEURS/B3_THEME.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
+          <t>Trois étapes séquentielles de l'entonnoir B3 (génération, audit, optimisation).</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr"/>
@@ -932,10 +932,14 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
+          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -969,43 +973,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>PASS_FUNNEL — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -1013,8 +990,8 @@
   <mergeCells count="5">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/_FACTORY/_LIGNES/_TEMPLATE/B3_DISTRACTEURS/B3_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/B3_DISTRACTEURS/B3_THEME.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISTRACTEURS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FLAGS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSAIRE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -656,44 +655,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Q_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>FLAG_TYPE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SEVERITY</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FIX_ACTION</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>STATUT_CORRECTION</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>QV-01-Q001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>COLLISION / FORMAT / PLAUSIBILITE / SPACING</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>[Description du problème]</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>EN_COURS / CORRIGÉ</t>
         </is>
@@ -702,298 +701,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>GLOSSAIRE — ÉTAPE B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Source : glossaire_documentaire_factory.md — LECTURE SEULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>TERME</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>DÉFINITION COURTE</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>RÈGLE PRINCIPALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>DISTRACTEUR</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Réponse incorrecte crédible proposée dans un QCM.</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-HB-DIST-002] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>POOL_COLLISION</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Réutilisation problématique d'un même angle dans plusieurs pools.</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>HARD_COLLISION</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Distractor identique à une réponse correcte ailleurs dans le pool.</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-HB-DIST-001] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>SOFT_COLLISION</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Même entité réutilisée dans contextes différents (réponse Q1, distractor Q2).</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-SW-DIST-001] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>PASS_FUNNEL</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Trois étapes séquentielles de l'entonnoir B3 (génération, audit, optimisation).</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>DECISION_GATE</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Mécanisme de validation B3 après PASS 2, avant PASS 3 ou export.</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-HB-DIST-004] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>PLAUSIBILITY_RATING</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Score subjectif (0-100%) ou catégorisé (LOW/MEDIUM/HIGH) de crédibilité d'un distractor.</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-SW-DIST-002] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>FORMAT_HOMOGENEITY</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Pourcentage de questions où réponse correcte + 3 distractors ont format identique.</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-HB-DIST-003] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>REUSE_RATE</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Pourcentage de distractors utilisés plus d'une fois inter-questions.</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-OPT-DIST-004] ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BIAS_DETECTION</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Détection de patterns de sur-représentation dans le pool de distracteurs.</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>STATUS_STANDARD</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Liste officielle des statuts documentaires autorisés.</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-STATUS-001] Tout autre format de statut est interdit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>QA_STATUS</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Résultat final des VALIDATIONS QA_STATUS.</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-QA-001] QA_STATUS=FAIL bloque l'export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>⚠ ALERTES — TERMES POTENTIELLEMENT MANQUANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>L'IA consigne ici tout terme utilisé dans cette étape mais absent du glossaire source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>